--- a/Codes_2025/Trial 3/Trial3_SVR_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_SVR_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>22.34</v>
       </c>
       <c r="D2" t="n">
-        <v>73.01718522136829</v>
+        <v>12.08107126704307</v>
       </c>
       <c r="E2" t="n">
-        <v>50.6771852213683</v>
+        <v>10.25892873295692</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>35.4</v>
       </c>
       <c r="D3" t="n">
-        <v>78.59645490886697</v>
+        <v>16.25589501149191</v>
       </c>
       <c r="E3" t="n">
-        <v>43.19645490886698</v>
+        <v>19.14410498850809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         <v>6.549999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>86.35547442466932</v>
+        <v>18.84910211819649</v>
       </c>
       <c r="E4" t="n">
-        <v>79.80547442466933</v>
+        <v>12.2991021181965</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>69.53000000000007</v>
       </c>
       <c r="D5" t="n">
-        <v>90.38341119554225</v>
+        <v>20.41934266874338</v>
       </c>
       <c r="E5" t="n">
-        <v>20.85341119554218</v>
+        <v>49.11065733125669</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>21.01</v>
+        <v>37.81</v>
       </c>
       <c r="D6" t="n">
-        <v>80.30049392311349</v>
+        <v>5.338493000607239</v>
       </c>
       <c r="E6" t="n">
-        <v>59.29049392311349</v>
+        <v>32.47150699939277</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>20.08</v>
+        <v>21.01</v>
       </c>
       <c r="D7" t="n">
-        <v>70.6289897176982</v>
+        <v>21.01993182494066</v>
       </c>
       <c r="E7" t="n">
-        <v>50.54898971769821</v>
+        <v>0.009931824940654366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D8" t="n">
-        <v>86.07529278772995</v>
+        <v>19.18253292000024</v>
       </c>
       <c r="E8" t="n">
-        <v>76.71529278772995</v>
+        <v>0.8974670799997568</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>7.180000000000001</v>
+        <v>6.81</v>
       </c>
       <c r="D9" t="n">
-        <v>87.99464286723529</v>
+        <v>6.537669551272018</v>
       </c>
       <c r="E9" t="n">
-        <v>80.81464286723528</v>
+        <v>0.2723304487279821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>37.67999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>95.33941989614358</v>
+        <v>21.76674744345307</v>
       </c>
       <c r="E10" t="n">
-        <v>57.65941989614359</v>
+        <v>12.40674744345307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>20.4824900567014</v>
+        <v>18.38097589869117</v>
       </c>
       <c r="E11" t="n">
-        <v>12.7524900567014</v>
+        <v>11.20097589869117</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.590000000000001</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>49.47683879245863</v>
+        <v>19.63607672506001</v>
       </c>
       <c r="E12" t="n">
-        <v>42.88683879245863</v>
+        <v>18.04392327493998</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>10.19</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="n">
-        <v>67.1805699190114</v>
+        <v>3.387328837136482</v>
       </c>
       <c r="E13" t="n">
-        <v>56.99056991901141</v>
+        <v>4.342671162863518</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,22 +751,94 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.26000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.615674611297757</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.64432538870225</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7.701350814123518</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.111350814123517</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>12.38504712424454</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.195047124244542</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>37.58000000000002</v>
       </c>
-      <c r="D14" t="n">
-        <v>49.88093836355381</v>
-      </c>
-      <c r="E14" t="n">
-        <v>12.30093836355379</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D17" t="n">
+        <v>15.79101591782166</v>
+      </c>
+      <c r="E17" t="n">
+        <v>21.78898408217836</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Leaders</t>
         </is>
